--- a/outputs/binder_sequences.xlsx
+++ b/outputs/binder_sequences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xiang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D852BF-3D81-4227-868F-667AD46A8072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E32C0E-2241-4132-A80E-27EF7B3B9CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
   <si>
     <t>Protein</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -261,6 +261,18 @@
   </si>
   <si>
     <t>*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fold4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>758</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIEEEAKTFLDKVNHELEDLLYKANLAKWNKSPEAEAALAALNAAVEKAMKEAKKFDLSKIKNPTVKKQLEILQNPELLKKVIDLLLNPVKGAWALGKGDFRIEPGVDKAEAEAVLAKYKKYAAQPIFLRGLAILEE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -377,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -405,6 +417,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EA7B05-3509-489A-9CC8-816FA4E3015E}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="112.9140625" customWidth="1"/>
@@ -724,7 +742,7 @@
         <v>36</v>
       </c>
       <c r="E2" s="1">
-        <f t="shared" ref="E2:E13" si="0">LEN(D2)</f>
+        <f t="shared" ref="E2:E14" si="0">LEN(D2)</f>
         <v>89</v>
       </c>
     </row>
@@ -888,6 +906,24 @@
       <c r="E13" s="1">
         <f t="shared" si="0"/>
         <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
